--- a/TestSet-0001/Test Cases.xlsx
+++ b/TestSet-0001/Test Cases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,8 +13,8 @@
     <sheet name="OrangeHRM Test Cases" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'bKash Test Cases'!$A$4:$J$14</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'OrangeHRM Test Cases'!$A$4:$J$9</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'bKash Test Cases'!$B$4:$K$14</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'OrangeHRM Test Cases'!$B$4:$K$9</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Test Scenarios'!$B$7:$G$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="133">
   <si>
     <t xml:space="preserve">Project Name</t>
   </si>
@@ -346,18 +346,138 @@
 PIN: Invalid</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">1. Login to bKash app
+    <t xml:space="preserve">1. Login to bKash app
 2. Select `Payment`
 3. Select `Tap to scan QR code`
 4. Scanner starts
 5. Capture the QR code in the camera
+4. The merchant’s name is displayed upon successful scanning
+5. Enter amount
+6. Confirm with invalid PIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transaction fails with an 'Invalid PIN' error message &amp;  the payment is unsuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_PAY_004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that a valid QR code works but PIN request fails due to invalid characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchant: XYZ Store
+Amount: 200 BDT
+PIN: Invalid with forbidden characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to bKash app
+2. Select `Payment`
+3. Select `Tap to scan QR code`
+4. Scanner starts
+5. Capture the QR code in the camera
+4. The merchant’s name is displayed upon successful scanning
+5. Enter amount
+6. Confirm with invalid PIN with forbidden characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transaction fails with an 'Invalid Characters' error message &amp;  the payment is unsuccessful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_ADD_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that adding an amount exceeding the maximum addition at once fails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank: DBBL
+Maximum Amount: 100000 BDT
+PIN: Valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to bKash app
+2. Navigate to 'Add Money'
+3. Select 'Bank to bKash'
+4. Select ‘Bank Account’
+5. Select ‘Saved Banks’
+6. Select the Bank from the list
+7. Enter amount exceeding the maximum limit
+8. Confirm with PIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum Amount exceeding warning is displayed &amp; the money is not added to the current balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_ADD_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that adding an amount lower than the minimum addition at once fails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank: DBBL
+Minimum Amount: 100 BDT
+PIN: Valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to bKash app
+2. Navigate to 'Add Money'
+3. Select 'Bank to bKash'
+4. Select ‘Bank Account’
+5. Select ‘Saved Banks’
+6. Select the Bank from the list
+7. Enter an amount more than 0 but less than the minimum limit
+8. Confirm with PIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insufficient addition warning is displayed &amp; the money is not added to the current balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OrangeHRM Test Cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that a leave application can not be made as no leave balance is available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. I am on URL: “https://opensource-demo.orangehrmlive.com/web/index.php/auth/login”
+2. I'm already registered
+3. I don't have any leave left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Username: “Admin”
+- Password: “admin123”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. I am on the target URL
+2. I enter Username in the Username field
+3. I enter Password in the Password field
+4. I press the Login button
+5. I am on the Dashboard page
+6. I click the 'Leave' option on the left sidebar
+7. I am on the 'Leave List' page
+8. I click the 'Apply' button at the top of the page
+9. I am on the 'Apply Leave' page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Leave Types with Leave Balance’ notice is displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that the application language remains ‘English’</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. I am on URL: “https://opensource-demo.orangehrmlive.com/web/index.php/leave/applyLeave”
 </t>
     </r>
     <r>
@@ -368,141 +488,29 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4. The merchant’s name is displayed upon successful scanning
-5. Enter amount
-6. Confirm with invalid PIN</t>
+      <t xml:space="preserve">2. I'm already registered
+3. I haven’t changed my in-app language to any other</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Transaction fails with an 'Invalid PIN' error message &amp;  the payment is unsuccessful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_PAY_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that a valid QR code works but PIN request fails due to invalid characters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merchant: XYZ Store
-Amount: 200 BDT
-PIN: Invalid with forbidden characters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to bKash app
-2. Select `Payment`
-3. Select `Tap to scan QR code`
-4. Scanner starts
-5. Capture the QR code in the camera
-4. The merchant’s name is displayed upon successful scanning
-5. Enter amount
-6. Confirm with invalid PIN with forbidden characters</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Transaction fails with an 'Invalid Characters' error message</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> &amp;  the payment is unsuccessful</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ADD_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that adding an amount exceeding the maximum addition at once fails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank: DBBL
-Maximum Amount: 100000 BDT
-PIN: Valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to bKash app
-2. Navigate to 'Add Money'
-3. Select 'Bank to bKash'
-4. Select ‘Bank Account’
-5. Select ‘Saved Banks’
-6. Select the Bank from the list
-7. Enter amount exceeding the maximum limit
-8. Confirm with PIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum Amount exceeding warning is displayed &amp; the money is not added to the current balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC_ADD_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that adding an amount lower than the minimum addition at once fails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank: DBBL
-Minimum Amount: 100 BDT
-PIN: Valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to bKash app
-2. Navigate to 'Add Money'
-3. Select 'Bank to bKash'
-4. Select ‘Bank Account’
-5. Select ‘Saved Banks’
-6. Select the Bank from the list
-7. Enter an amount more than 0 but less than the minimum limit
-8. Confirm with PIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insufficient addition warning is displayed &amp; the money is not added to the current balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OrangeHRM Test Cases (Automation Suite)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that a leave application can not be made as no leave balance is available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- I am on URL: “https://opensource-demo.orangehrmlive.com/web/index.php/auth/login”
-- I'm already registered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- My Username: “Admin”
-- My Password: “admin123”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. I go to the target URL
-2. I enter my Username in the Username field
-3. I enter my Password in the Password field
+    <t xml:space="preserve">1. I am on the target URL
+2. I enter Username in the Username field
+3. I enter Password in the Password field
 4. I press the Login button
 5. I am on the Dashboard page
-6. I click the 'Leave' option on the left sidebar
-7. I am on the 'Leave List' page
-8. I click the 'Apply' button at the top of the page
-9. I am on the 'Apply Leave' page
-10. It says "No Leave Types with Leave Balance" in the "Apply Leave" section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Leave Types with Leave Balance’ notice is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL_002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that the application language remains ‘English’</t>
+6. I see the application language is English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Language is English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Application Language should be English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that I can’t apply for a leave with invalid date range</t>
   </si>
   <si>
     <r>
@@ -513,7 +521,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">- I am on URL: “https://opensource-demo.orangehrmlive.com/web/index.php/leave/applyLeave”
+      <t xml:space="preserve">1. I am on URL: “https://opensource-demo.orangehrmlive.com/web/index.php/leave/applyLeave”
 </t>
     </r>
     <r>
@@ -524,40 +532,72 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">- I'm already registered
-- I haven’t changed my in-app language to any other</t>
+      <t xml:space="preserve">2. I'm already registered
+3. </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">1. I go to the target URL
-2. I enter my Username in the Username field
-3. I enter my Password in the Password field
-4. I press the Login button
-5. I am on the Dashboard page
-6. I see the application language is English</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Language is not in English</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Application Language should be in  English</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that I can’t apply for a leave with invalid date range</t>
-  </si>
-  <si>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">I have leaves left</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. I am on the target URL
+2. I enter Username in the Username field
+3. I enter Password in the Password field
+4. I press the Login button
+5. I am on the 'Apply Leave' page
+6. I select a date in the ‘From Date’ field
+7. I select a prior date than the ‘From Date’ in the ‘To Date’ field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Warning saying saying “To date should be after from date” is displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A warning saying “To date should be after from date” under the ‘To Date’ field should be displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL_004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that I can’t apply for leave to a prior date than today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. I am on the target URL
+2. I enter Username in the Username field
+3. I enter Password in the Password field
+4. I press the Login button
+5. I am on the 'Apply Leave' page
+6. I select a prior date from today in the ‘From Date’ field
+7. I select a prior date than the ‘From Date’ in the ‘To Date’ field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under the leave balance, a warning saying “Balance not sufficient” is displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under the leave balance, a warning saying “Balance not sufficient” should be displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AL_005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that a leave application can be made with valid data</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">- I am on URL: “https://opensource-demo.orangehrmlive.com/web/index.php/leave/applyLeave”
+      <t xml:space="preserve">1. I am on URL: “https://opensource-demo.orangehrmlive.com/web/index.php/auth/login”
+2. I'm already registered
 </t>
     </r>
     <r>
@@ -566,107 +606,26 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">- I'm already registered</t>
+      <t xml:space="preserve">3. I have leaves left</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">1. I go to the target URL
-2. I enter my Username in the Username field
-3. I enter my Password in the Password field
-4. I press the Login button
-5. I am on the 'Apply Leave' page
-6. I select a date in the ‘From Date’ field
-7. I select a prior date than the ‘From Date’ in the ‘To Date’ field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Warning saying saying “To date should be after from date” is displayed </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A warning saying “To date should be after from date” under the ‘To Date’ field should be displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that I can’t apply for leave to a prior date than today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. I go to the target URL
-2. I enter my Username in the Username field
-3. I enter my Password in the Password field
-4. I press the Login button
-5. I am on the 'Apply Leave' page
-6. I select a prior date from today in the ‘From Date’ field
-7. I select a prior date than the ‘From Date’ in the ‘To Date’ field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under the leave balance, a warning saying “Balance not sufficient” is displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under the leave balance, a warning saying “Balance not sufficient” should be displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify that a leave application can be made with valid data</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. I go to the target URL
-2. I enter my Username in the Username field
-3. I enter my Password in the Password field
+    <t xml:space="preserve">1. I am on the target URL
+2. I enter Username in the Username field
+3. I enter Password in the Password field
 4. I press the Login button
 5. I am on the Dashboard page
 6. I click the 'Leave' option on the left sidebar
 7. I am on the 'Leave List' page
 8. I click the 'Apply' button at the top of the page
 9. I am on the 'Apply Leave' page
-10. I click on the</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Leave Type Dropdown Arrow
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11. I select a vacation type from the Leave Type Dropdown List
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12. I pick a future date than the ‘From Date’ field
+10. I click on the Leave Type Dropdown Arrow
+11. I select a vacation type from the Leave Type Dropdown List
+12. I pick a future date than the ‘From Date’ field
 13. I pick a future date further to the ‘From Date’ from the ‘To Date’ field
 14. I write a comment in the ‘Comments’ field.
 15. I click on ‘Apply’</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">An application submission success pop-up in green is displayed</t>
@@ -682,7 +641,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -729,7 +688,13 @@
     <font>
       <b val="true"/>
       <sz val="20"/>
-      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -740,28 +705,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -770,32 +715,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8CB"/>
-        <bgColor rgb="FFDDDDDD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFDDE8CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9211E"/>
-        <bgColor rgb="FF993366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFDDE8CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF5429"/>
-        <bgColor rgb="FFFF8080"/>
+        <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -840,7 +761,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -853,38 +774,34 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -901,39 +818,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -950,27 +863,11 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDDDDDD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDDE8CB"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -985,7 +882,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEEEEEE"/>
+          <fgColor rgb="FF000000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1011,7 +908,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFEEEEEE"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1027,7 +924,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFDDE8CB"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1038,14 +935,14 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF5429"/>
+      <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFC9211E"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -1177,11 +1074,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G20"/>
+  <dimension ref="B2:G13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.79"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="41.46"/>
@@ -1373,9 +1270,6 @@
       <c r="G13" s="8" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="B7:G11"/>
@@ -1403,35 +1297,36 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="B1:L14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="10" width="21.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="10" width="36.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="10" width="32.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="8.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="10" width="27.26"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="10" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="7.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="13.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="5" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="36.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="5" width="32.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="8.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="27.26"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="9" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="5" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="14"/>
-    </row>
-    <row r="2" customFormat="false" ht="24.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" s="14" customFormat="true" ht="24.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="15"/>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
@@ -1440,384 +1335,409 @@
       <c r="H2" s="15"/>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="E4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="F4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="G4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="H4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="I4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="J4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="K4" s="6" t="s">
         <v>42</v>
       </c>
+      <c r="L4" s="16" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="B5" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="C5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="G5" s="17" t="s">
         <v>47</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>48</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="K5" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="B6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="G6" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="H6" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="I6" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="J6" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="K6" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="20"/>
+      <c r="L6" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="B7" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="E7" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="F7" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="G7" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>64</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="K7" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="20"/>
+      <c r="L7" s="19" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="B8" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="C8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="D8" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="E8" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="G8" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="H8" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="I8" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="J8" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="K8" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="K8" s="20"/>
+      <c r="L8" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="B9" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="C9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="G9" s="17" t="s">
         <v>76</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>77</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="K9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="20"/>
+      <c r="L9" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+      <c r="B10" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="C10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="D10" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="E10" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="F10" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="G10" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="H10" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="I10" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="J10" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="17" t="s">
+      <c r="K10" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="20"/>
+      <c r="L10" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+      <c r="B11" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="C11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="D11" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="E11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="F11" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="G11" s="17" t="s">
         <v>86</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>87</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="17" t="s">
+      <c r="K11" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="K11" s="20"/>
+      <c r="L11" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="C12" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="D12" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="E12" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="F12" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="G12" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="H12" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="I12" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="J12" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="K12" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="K12" s="20"/>
+      <c r="L12" s="19" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
+      <c r="B13" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="C13" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="D13" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="E13" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="F13" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="G13" s="17" t="s">
         <v>96</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>97</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J13" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="K13" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="20"/>
+      <c r="L13" s="19" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+      <c r="B14" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="C14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="E14" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="F14" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="G14" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="H14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="I14" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="J14" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="K14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="20"/>
+      <c r="L14" s="19" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J14"/>
+  <autoFilter ref="B4:K14"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B2:L2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
@@ -1835,225 +1755,242 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="B1:M13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="15.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="14.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="10" width="21.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="10" width="36.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="10" width="32.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="8.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="10" width="27.26"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="10" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="7.93"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="14.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="5" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="36.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="5" width="32.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="8.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="5" width="27.26"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="5" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="14"/>
-    </row>
-    <row r="2" customFormat="false" ht="24.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" s="14" customFormat="true" ht="24.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="E4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="F4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="G4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="H4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="I4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="J4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="K4" s="6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="L4" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="G5" s="17" t="s">
         <v>108</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>109</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="94.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="B6" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="C6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="E6" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="G6" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="H6" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="I6" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="I6" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="17"/>
-    </row>
-    <row r="7" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="J6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="17"/>
+      <c r="L6" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="C7" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="D7" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="E7" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="F7" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="G7" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="H7" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="I7" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="J7" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="17"/>
-    </row>
-    <row r="8" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="K7" s="17"/>
+      <c r="L7" s="19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="C8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="D8" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="E8" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="G8" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="H8" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="I8" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="J8" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" customFormat="false" ht="275.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="K8" s="17"/>
+      <c r="L8" s="19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="C9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>106</v>
-      </c>
       <c r="E9" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>107</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>129</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>130</v>
@@ -2061,18 +1998,24 @@
       <c r="H9" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="J9" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="19" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="24"/>
+      <c r="F13" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J9"/>
+  <autoFilter ref="B4:K9"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B2:L2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
